--- a/artfynd/A 7862-2024 artfynd.xlsx
+++ b/artfynd/A 7862-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117845202</v>
+        <v>132461971</v>
       </c>
       <c r="B2" t="n">
-        <v>96108</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramnsjön, 300 m NV, Sk</t>
+          <t>holmgången, Vittsjö, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416820</v>
+        <v>416496</v>
       </c>
       <c r="R2" t="n">
-        <v>6246290</v>
+        <v>6246339</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,27 +772,604 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126746365</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58039</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>holmgången, Vittsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>416496</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6246339</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132461942</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>holmgången, Vittsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>416496</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6246339</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132461909</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>holmgången, Vittsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>416496</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6246339</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>107618546</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>holmgången, Vittsjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>416496</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6246339</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-03-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-03-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stefan Havsvik</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117845202</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97733</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ramnsjön, 300 m NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>416820</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6246290</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Crister Albinsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Crister Albinsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7862-2024 artfynd.xlsx
+++ b/artfynd/A 7862-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117845202</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132461971</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126746365</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132461942</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132461909</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,8 +1400,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107618546</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>